--- a/output/hrv/male_HFD_HRV_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
+++ b/output/hrv/male_HFD_HRV_ECG_calculated_num_k_is_50_kmax_is_20_window_step_is_None.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\ECGBiologicalAge\HeartAge\output\hrv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACC77E7B-0523-4588-8A0B-781646D60F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50507D99-F9C8-4F8E-BF23-512CD49F5BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{902BDADF-5C85-420F-AA22-D2170F70FB29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{C4929B81-05BB-4E3E-B745-2D2F67EE8668}"/>
   </bookViews>
   <sheets>
     <sheet name="male_HFD_HRV_ECG_calculated_num" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>20 - 24</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>65 - 69</t>
-  </si>
-  <si>
-    <t>80 - 84</t>
   </si>
 </sst>
 </file>
@@ -687,9 +684,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>male_HFD_HRV_ECG_calculated_num!$A$1:$A$13</c:f>
+              <c:f>male_HFD_HRV_ECG_calculated_num!$A$1:$A$12</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>18 - 19</c:v>
                 </c:pt>
@@ -725,57 +722,51 @@
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>70 - 74</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>80 - 84</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>male_HFD_HRV_ECG_calculated_num!$B$1:$B$13</c:f>
+              <c:f>male_HFD_HRV_ECG_calculated_num!$B$1:$B$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>1.9430000000000001</c:v>
+                  <c:v>1.9510000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9410000000000001</c:v>
+                  <c:v>1.9510000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1.952</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.948</c:v>
+                  <c:v>1.9610000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.952</c:v>
+                  <c:v>1.96</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1.964</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.944</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.9430000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>1.9470000000000001</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.875</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.919</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.925</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.8779999999999999</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.9159999999999999</c:v>
+                  <c:v>1.95</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.92</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1.984</c:v>
+                  <c:v>1.9379999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -783,7 +774,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2308-452E-AF93-A9E25C7631B1}"/>
+              <c16:uniqueId val="{00000000-E27A-4C7F-8054-92843EBF1087}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -796,11 +787,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1493293216"/>
-        <c:axId val="1493296096"/>
+        <c:axId val="629471504"/>
+        <c:axId val="629473424"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1493293216"/>
+        <c:axId val="629471504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -843,7 +834,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1493296096"/>
+        <c:crossAx val="629473424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -851,7 +842,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1493296096"/>
+        <c:axId val="629473424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -902,7 +893,7 @@
             <a:endParaRPr lang="uk-UA"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1493293216"/>
+        <c:crossAx val="629471504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1518,14 +1509,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>533399</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>152401</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>9524</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>90487</xdr:rowOff>
     </xdr:to>
@@ -1534,7 +1525,7 @@
         <xdr:cNvPr id="2" name="Діаграма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BBD8882-3ABF-707D-6977-E16865E1FD17}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BE46EF3-CF5C-FB74-560F-E0362297DD28}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1871,8 +1862,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55B22DD3-A09E-4F83-997B-D17482BD00A1}">
-  <dimension ref="A1:B13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F9037F-7BC3-4C33-AD5A-DCAED461FAC4}">
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1880,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="B1">
-        <v>1.9430000000000001</v>
+        <v>1.9510000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1888,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>1.9410000000000001</v>
+        <v>1.9510000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1904,7 +1895,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1.948</v>
+        <v>1.9610000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1912,7 +1903,7 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>1.952</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1920,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>1.9470000000000001</v>
+        <v>1.964</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1928,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>1.875</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1936,7 +1927,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1.919</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1944,7 +1935,7 @@
         <v>2</v>
       </c>
       <c r="B9">
-        <v>1.925</v>
+        <v>1.9430000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1952,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>1.8779999999999999</v>
+        <v>1.9470000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1960,7 +1951,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1.9159999999999999</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1968,20 +1959,12 @@
         <v>6</v>
       </c>
       <c r="B12">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>1.984</v>
+        <v>1.9379999999999999</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B13">
-    <sortCondition ref="A1:A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B12">
+    <sortCondition ref="A1:A12"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
